--- a/references/clearance/SI-public.xlsx
+++ b/references/clearance/SI-public.xlsx
@@ -17,13 +17,27 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="14"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
   </fonts>
   <fills count="2">
@@ -34,7 +48,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -42,12 +56,38 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="00000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -413,264 +453,329 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="24" customWidth="1" min="1" max="1"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
+  </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>BOOKING / SHIPPING INSTRUCTION (SI)</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" s="2" t="inlineStr">
         <is>
           <t>（订舱补料 — 非提单正本；正本由船公司签发）</t>
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" s="3" t="inlineStr">
         <is>
           <t>SHIPPER</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="B4" s="3" t="inlineStr">
         <is>
           <t>{{COMPANY_NAME_EN}}</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C4" s="3" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr"/>
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>{{COMPANY_ADDR_EN}}</t>
         </is>
       </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="C5" s="2" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
         <is>
           <t>CONSIGNEE</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="B6" s="3" t="inlineStr">
         <is>
           <t>{{CONSIGNEE_NAME}}</t>
         </is>
       </c>
-      <c r="C5" t="inlineStr">
+      <c r="C6" s="3" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr"/>
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>{{CONSIGNEE_ADDR}}</t>
         </is>
       </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="C7" s="2" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
         <is>
           <t>NOTIFY</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
+      <c r="B8" s="3" t="inlineStr">
         <is>
           <t>{{NOTIFY}}</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr">
+      <c r="C8" s="3" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr"/>
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>{{NOTIFY_ADDR}}</t>
         </is>
       </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="C9" s="2" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
         <is>
           <t>DESTINATION AGENT</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="B10" s="3" t="inlineStr">
         <is>
           <t>{{DEST_AGENT_NAME}}</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr">
+      <c r="C10" s="3" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr"/>
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>{{DEST_AGENT_ADDR}}</t>
         </is>
       </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>{{DEST_AGENT_TAX}}</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>{{DEST_AGENT_TEL}}</t>
-        </is>
-      </c>
-    </row>
-    <row r="9"/>
-    <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="C11" s="2" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr"/>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>{{DEST_AGENT_TAX}} {{DEST_AGENT_TEL}}</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
         <is>
           <t>VESSEL / VOYAGE</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="B14" s="3" t="inlineStr">
         <is>
           <t>{{VESSEL}}</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="C14" s="3" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
         <is>
           <t>B/L NO.</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
+      <c r="B15" s="3" t="inlineStr">
         <is>
           <t>{{BL_NO}}</t>
         </is>
       </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="C15" s="3" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
         <is>
           <t>PORT OF LOADING</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>{{LOADING_PORT}}</t>
         </is>
       </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="C16" s="3" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
         <is>
           <t>PORT OF DISCHARGE</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
+      <c r="B17" s="3" t="inlineStr">
         <is>
           <t>{{DISCHARGE_PORT}}</t>
         </is>
       </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C17" s="3" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
         <is>
           <t>CONTAINER NO.</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="B18" s="3" t="inlineStr">
         <is>
           <t>{{CONTAINER_NO}}</t>
         </is>
       </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="C18" s="3" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
         <is>
           <t>SEAL NO.</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
+      <c r="B19" s="3" t="inlineStr">
         <is>
           <t>{{SEAL_NO}}</t>
         </is>
       </c>
-    </row>
-    <row r="16"/>
-    <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="C19" s="3" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>DESCRIPTION</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>{{ITEM_DESC}}</t>
         </is>
       </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="C21" s="3" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
         <is>
           <t>QTY / NET WEIGHT</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>{{SHIPPED_QTY}}</t>
         </is>
       </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="C22" s="3" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>H.S. CODE</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>{{HS_CODES}}</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="C23" s="3" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
         <is>
           <t>PACKAGES</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>{{TOTALS_LINE}}</t>
         </is>
       </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="C24" s="3" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
         <is>
           <t>GROSS WEIGHT (KGS)</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>{{GROSS_KG}}</t>
         </is>
       </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="C25" s="3" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
         <is>
           <t>MEASUREMENT (CBM)</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>{{VOLUME_CBM}}</t>
         </is>
       </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="C26" s="3" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>FREIGHT</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>FREIGHT PREPAID</t>
         </is>
       </c>
+      <c r="C27" s="3" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>{{COMPANY_NAME_EN}}</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <mergeCells count="25">
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B7:C7"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="B22:C22"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="A2:C2"/>
+    <mergeCell ref="B12:C12"/>
+    <mergeCell ref="B21:C21"/>
+    <mergeCell ref="B11:C11"/>
+    <mergeCell ref="B23:C23"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A29:C29"/>
+    <mergeCell ref="B8:C8"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="B10:C10"/>
+    <mergeCell ref="B9:C9"/>
+    <mergeCell ref="B6:C6"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="B5:C5"/>
+    <mergeCell ref="B26:C26"/>
+    <mergeCell ref="B4:C4"/>
+  </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>